--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484372_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484372_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4181</v>
+        <v>6.3402</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1611</v>
+        <v>4.4644</v>
       </c>
       <c r="F2" t="n">
-        <v>2.257</v>
+        <v>1.8757</v>
       </c>
       <c r="G2" t="n">
         <v>3.2956</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06759999999999999</v>
+        <v>-0.0103</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8198</v>
+        <v>-0.5164</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8874</v>
+        <v>0.5061</v>
       </c>
       <c r="V2" t="n">
         <v>1.8828</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8736</v>
+        <v>6.3288</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3446</v>
+        <v>3.4457</v>
       </c>
       <c r="F3" t="n">
-        <v>2.529</v>
+        <v>2.8831</v>
       </c>
       <c r="G3" t="n">
         <v>4.2194</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7131</v>
+        <v>-0.258</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5777</v>
+        <v>-0.4766</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1354</v>
+        <v>0.2186</v>
       </c>
       <c r="V3" t="n">
         <v>0.6093</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2279</v>
+        <v>5.794</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5528</v>
+        <v>4.1189</v>
       </c>
       <c r="F4" t="n">
         <v>1.6751</v>
@@ -766,10 +766,10 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3164</v>
+        <v>0.2497</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6849</v>
+        <v>-0.1189</v>
       </c>
       <c r="U4" t="n">
         <v>0.3686</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0111</v>
+        <v>3.3448</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1327</v>
+        <v>2.5753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8784</v>
+        <v>0.7695</v>
       </c>
       <c r="G5" t="n">
         <v>0.6568000000000001</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5962</v>
+        <v>0.93</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3003</v>
+        <v>0.743</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2959</v>
+        <v>0.187</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2272</v>
+        <v>3.1873</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6569</v>
+        <v>1.3838</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5703</v>
+        <v>1.8035</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2325</v>
+        <v>1.8626</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7199</v>
+        <v>0.3515</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5125999999999999</v>
+        <v>1.511</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7131</v>
+        <v>1.6727</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2786</v>
+        <v>1.1051</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5655</v>
+        <v>0.5675</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5195</v>
+        <v>0.1899</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5587</v>
+        <v>-0.7536</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0782</v>
+        <v>0.9435</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.236</v>
+        <v>-0.0427</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0246</v>
+        <v>-0.2888</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2114</v>
+        <v>0.2462</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.16</v>
+        <v>3.0133</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3838</v>
+        <v>2.2524</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7762</v>
+        <v>0.7609</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8626</v>
+        <v>4.2325</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3515</v>
+        <v>3.7199</v>
       </c>
       <c r="I7" t="n">
-        <v>1.511</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6727</v>
+        <v>3.7131</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1051</v>
+        <v>4.2786</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5675</v>
+        <v>-0.5655</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1899</v>
+        <v>0.5195</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7536</v>
+        <v>-0.5587</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9435</v>
+        <v>1.0782</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0699</v>
+        <v>-0.4499</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2888</v>
+        <v>-0.4291</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2189</v>
+        <v>-0.0208</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8159</v>
+        <v>2.3648</v>
       </c>
       <c r="E8" t="n">
-        <v>2.255</v>
+        <v>1.7494</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5609</v>
+        <v>0.6153</v>
       </c>
       <c r="G8" t="n">
         <v>1.6222</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9938</v>
+        <v>0.5427</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2272</v>
+        <v>0.7216</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7768</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.652</v>
+        <v>1.9826</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4341</v>
+        <v>0.7375</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2179</v>
+        <v>1.2451</v>
       </c>
       <c r="G9" t="n">
         <v>2.0851</v>
@@ -1156,13 +1156,13 @@
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8237</v>
+        <v>-0.4932</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9408</v>
+        <v>-0.6375</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1171</v>
+        <v>0.1443</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.374</v>
+        <v>1.5481</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1562</v>
+        <v>1.3342</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5301</v>
+        <v>0.2139</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4732</v>
+        <v>0.2673</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9726</v>
+        <v>-1.9177</v>
       </c>
       <c r="I10" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.0398</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.5898</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.7725</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.3676</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.4994</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.9646</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.6346000000000001</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-1.4379</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1.3026</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.1352</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2845</v>
-      </c>
       <c r="T10" t="n">
-        <v>-0.4566</v>
+        <v>0.2711</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7411</v>
+        <v>0.2283</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.663</v>
+        <v>1.236</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6669</v>
+        <v>0.0055</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.004</v>
+        <v>1.2306</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2673</v>
+        <v>-0.4732</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9177</v>
+        <v>-0.9726</v>
       </c>
       <c r="I11" t="n">
-        <v>2.185</v>
+        <v>0.4994</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0398</v>
+        <v>0.9646</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.55</v>
+        <v>0.33</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5898</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7725</v>
+        <v>-1.4379</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3676</v>
+        <v>-1.3026</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4049</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3857</v>
+        <v>0.1465</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3961</v>
+        <v>-0.295</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0104</v>
+        <v>0.4415</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3647</v>
+        <v>0.3763</v>
       </c>
       <c r="E12" t="n">
-        <v>0.192</v>
+        <v>0.3942</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1728</v>
+        <v>-0.0179</v>
       </c>
       <c r="G12" t="n">
         <v>0.3316</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2757</v>
+        <v>-0.2641</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4842</v>
+        <v>-0.282</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2085</v>
+        <v>0.0178</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4311</v>
+        <v>-1.8572</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5148</v>
+        <v>-2.0498</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1926</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8219</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3786</v>
+        <v>0.1953</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2145</v>
+        <v>0.2504</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.164</v>
+        <v>-0.0551</v>
       </c>
       <c r="V13" t="n">
         <v>0.9414</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>33.3564</v>
+        <v>33.659</v>
       </c>
       <c r="E14" t="n">
-        <v>20.1089</v>
+        <v>20.4115</v>
       </c>
       <c r="F14" t="n">
-        <v>13.2473</v>
+        <v>13.2474</v>
       </c>
       <c r="G14" t="n">
         <v>19.6773</v>
@@ -1525,7 +1525,7 @@
         <v>17.1923</v>
       </c>
       <c r="L14" t="n">
-        <v>8.1</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-5.6152</v>
@@ -1543,16 +1543,16 @@
         <v>-7.813599999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>19.53429999999999</v>
+        <v>19.5343</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7429999999999999</v>
+        <v>1.0454</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3605</v>
+        <v>-1.0582</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1038</v>
+        <v>2.1036</v>
       </c>
       <c r="V14" t="n">
         <v>1.2157</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.2953</v>
       </c>
       <c r="E15" t="n">
         <v>0.8663999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7877</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.0613</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5453</v>
+        <v>-0.3288</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2888</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2565</v>
+        <v>-0.04</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2186</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8881</v>
+        <v>-0.5744</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5309</v>
+        <v>-0.8132</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4191</v>
+        <v>0.2388</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.082</v>
+        <v>-1.5879</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5615</v>
+        <v>1.3927</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.5205</v>
+        <v>-2.9806</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7727000000000001</v>
+        <v>1.0884</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8023</v>
+        <v>3.6634</v>
       </c>
       <c r="L16" t="n">
         <v>-2.575</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.3093</v>
+        <v>-2.6763</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.3638</v>
+        <v>-2.2707</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9455</v>
+        <v>-0.4056</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0301</v>
+        <v>0.4395</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0347</v>
+        <v>-0.3073</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0046</v>
+        <v>0.7468</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3824</v>
+        <v>1.5507</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6596</v>
+        <v>0.5545</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0684</v>
+        <v>-1.3859</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7121</v>
+        <v>1.5198</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3563</v>
+        <v>-2.9057</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5879</v>
+        <v>-5.082</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3927</v>
+        <v>-1.5615</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9806</v>
+        <v>-3.5205</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0884</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6634</v>
+        <v>1.8023</v>
       </c>
       <c r="L17" t="n">
         <v>-2.575</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6763</v>
+        <v>-4.3093</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2707</v>
+        <v>-3.3638</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4056</v>
+        <v>-0.9455</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="R17" t="n">
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0545</v>
+        <v>0.5324</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2062</v>
+        <v>0.0236</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1517</v>
+        <v>0.5088</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5507</v>
+        <v>2.3824</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5545</v>
+        <v>2.6596</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9962</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.4265</v>
+        <v>-3.3453</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8278</v>
+        <v>-1.4233</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5987</v>
+        <v>-1.9219</v>
       </c>
       <c r="G18" t="n">
         <v>-4.194</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6466</v>
+        <v>0.4347</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6244</v>
+        <v>-0.22</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0221</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.6093</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.5137</v>
+        <v>-4.3064</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6235</v>
+        <v>-3.5224</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8902</v>
+        <v>-0.784</v>
       </c>
       <c r="G19" t="n">
         <v>-3.752</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0622</v>
+        <v>0.1452</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5172</v>
+        <v>-0.416</v>
       </c>
       <c r="U19" t="n">
-        <v>0.455</v>
+        <v>0.5612</v>
       </c>
       <c r="V19" t="n">
         <v>0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.191</v>
+        <v>-5.9408</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5585</v>
+        <v>-3.6596</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6325</v>
+        <v>-2.2812</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3625</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2031</v>
+        <v>0.4533</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0108</v>
+        <v>-0.112</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2139</v>
+        <v>0.5653</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8828</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.5873</v>
+        <v>-7.2764</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1952</v>
+        <v>-2.6896</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.392</v>
+        <v>-4.5868</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4947</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1231</v>
+        <v>0.434</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9876</v>
+        <v>-0.482</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1107</v>
+        <v>0.916</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9414</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.76</v>
+        <v>-8.126099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0634</v>
+        <v>-2.8612</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.6966</v>
+        <v>-5.2649</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2653</v>
@@ -2170,13 +2170,13 @@
         <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.1568</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5034</v>
+        <v>-0.3012</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2874</v>
+        <v>0.1443</v>
       </c>
       <c r="V22" t="n">
         <v>-1.9925</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-33.3563</v>
+        <v>-30.66</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.5832</v>
+        <v>-12.5831</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.7731</v>
+        <v>-18.0768</v>
       </c>
       <c r="G23" t="n">
         <v>-19.6771</v>
@@ -2248,13 +2248,13 @@
         <v>7.8137</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7430999999999999</v>
+        <v>1.9535</v>
       </c>
       <c r="T23" t="n">
         <v>-2.1037</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3607</v>
+        <v>4.0571</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2157</v>
@@ -2263,7 +2263,7 @@
         <v>3.4395</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.655200000000001</v>
+        <v>-4.6552</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484372_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484372_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,31 +736,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.794</v>
+        <v>4.273</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1189</v>
+        <v>2.5979</v>
       </c>
       <c r="F4" t="n">
         <v>1.6751</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3993</v>
+        <v>1.8783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4587</v>
+        <v>0.1517</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9406</v>
+        <v>1.7266</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2377</v>
+        <v>2.7167</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7012</v>
+        <v>1.3942</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5365</v>
+        <v>1.3225</v>
       </c>
       <c r="M4" t="n">
         <v>-0.8384</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1127</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.236</v>
+        <v>1.521</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0055</v>
+        <v>1.521</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2306</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4732</v>
+        <v>1.521</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9726</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4994</v>
+        <v>1.214</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9646</v>
+        <v>1.521</v>
       </c>
       <c r="K11" t="n">
-        <v>0.33</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6346000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4379</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3026</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1352</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1465</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.295</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4415</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. ARRANZ JARAMILLO</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3763</v>
+        <v>1.236</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3942</v>
+        <v>0.0055</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0179</v>
+        <v>1.2306</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3316</v>
+        <v>-0.4732</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8307</v>
+        <v>-0.9726</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.499</v>
+        <v>0.4994</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6762</v>
+        <v>0.9646</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3098</v>
+        <v>0.33</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3445</v>
+        <v>-1.4379</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4792</v>
+        <v>-1.3026</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1346</v>
+        <v>-0.1352</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2641</v>
+        <v>0.1465</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.282</v>
+        <v>-0.295</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0178</v>
+        <v>0.4415</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>N. ARRANZ JARAMILLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8572</v>
+        <v>0.3763</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0498</v>
+        <v>0.3942</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1926</v>
+        <v>-0.0179</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8219</v>
+        <v>0.3316</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5529</v>
+        <v>0.8307</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.269</v>
+        <v>-0.499</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5887</v>
+        <v>0.6762</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5897</v>
+        <v>1.3098</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2332</v>
+        <v>-0.3445</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.4792</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.27</v>
+        <v>0.1346</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1953</v>
+        <v>-0.2641</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2504</v>
+        <v>-0.282</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0551</v>
+        <v>0.0178</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>33.659</v>
+        <v>-1.8572</v>
       </c>
       <c r="E14" t="n">
-        <v>20.4115</v>
+        <v>-2.0498</v>
       </c>
       <c r="F14" t="n">
-        <v>13.2474</v>
+        <v>0.1926</v>
       </c>
       <c r="G14" t="n">
-        <v>19.6773</v>
+        <v>-1.8219</v>
       </c>
       <c r="H14" t="n">
-        <v>6.8624</v>
+        <v>-1.5529</v>
       </c>
       <c r="I14" t="n">
-        <v>12.8148</v>
+        <v>-0.269</v>
       </c>
       <c r="J14" t="n">
-        <v>25.2924</v>
+        <v>-0.5887</v>
       </c>
       <c r="K14" t="n">
-        <v>17.1923</v>
+        <v>-0.5897</v>
       </c>
       <c r="L14" t="n">
-        <v>8.100000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.6152</v>
+        <v>-1.2332</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.3299</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>4.714700000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="P14" t="n">
-        <v>11.7206</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.813599999999999</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>19.5343</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0454</v>
+        <v>0.1953</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0582</v>
+        <v>0.2504</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1036</v>
+        <v>-0.0551</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2157</v>
+        <v>0.9414</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9908</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7753</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2953</v>
+        <v>33.659</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8663999999999999</v>
+        <v>20.4115</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5711000000000001</v>
+        <v>13.2474</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0613</v>
+        <v>19.6773</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4359</v>
+        <v>6.8624</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4972</v>
+        <v>12.8148</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3506</v>
+        <v>25.2924</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1228</v>
+        <v>17.1923</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2278</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2893</v>
+        <v>-5.6152</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5587</v>
+        <v>-10.3299</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2694</v>
+        <v>4.714700000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>11.7206</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-7.813599999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>19.5343</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3288</v>
+        <v>1.0454</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2888</v>
+        <v>-1.0582</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.04</v>
+        <v>2.1036</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>1.2157</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.9908</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-2.7753</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5744</v>
+        <v>2.4489</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8132</v>
+        <v>2.4489</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2388</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5879</v>
+        <v>2.4489</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3927</v>
+        <v>1.8419</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9806</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0884</v>
+        <v>2.4489</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6634</v>
+        <v>1.8419</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.575</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6763</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2707</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4056</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4395</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3073</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7468</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9962</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3859</v>
+        <v>0.2953</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5198</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9057</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.082</v>
+        <v>1.0613</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5615</v>
+        <v>-0.4359</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.5205</v>
+        <v>1.4972</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7727000000000001</v>
+        <v>1.3506</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8023</v>
+        <v>0.1228</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.575</v>
+        <v>1.2278</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.3093</v>
+        <v>-0.2893</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.3638</v>
+        <v>-0.5587</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9455</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
         <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5324</v>
+        <v>-0.3288</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0236</v>
+        <v>-0.2888</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5088</v>
+        <v>-0.04</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3824</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6596</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3453</v>
+        <v>-0.5744</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4233</v>
+        <v>-0.8132</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9219</v>
+        <v>0.2388</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.194</v>
+        <v>-1.5879</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6444</v>
+        <v>1.3927</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5495</v>
+        <v>-2.9806</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3086</v>
+        <v>1.0884</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3517</v>
+        <v>3.6634</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6603</v>
+        <v>-2.575</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.8854</v>
+        <v>-2.6763</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9962</v>
+        <v>-2.2707</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8893</v>
+        <v>-0.4056</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4347</v>
+        <v>0.4395</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.22</v>
+        <v>-0.3073</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.7468</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6093</v>
+        <v>1.5507</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>0.9962</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.3064</v>
+        <v>-1.3859</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5224</v>
+        <v>1.5198</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.784</v>
+        <v>-2.9057</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.752</v>
+        <v>-5.082</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9852</v>
+        <v>-1.5615</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7669</v>
+        <v>-3.5205</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4302</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2034</v>
+        <v>1.8023</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2268</v>
+        <v>-2.575</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3219</v>
+        <v>-4.3093</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7818</v>
+        <v>-3.3638</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5401</v>
+        <v>-0.9455</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1452</v>
+        <v>0.5324</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.416</v>
+        <v>0.0236</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5612</v>
+        <v>0.5088</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2772</v>
+        <v>2.3824</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>2.6596</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.9408</v>
+        <v>-3.3453</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6596</v>
+        <v>-1.4233</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2812</v>
+        <v>-1.9219</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3625</v>
+        <v>-4.194</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3937</v>
+        <v>-1.6444</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9688</v>
+        <v>-2.5495</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0352</v>
+        <v>-0.3086</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7188</v>
+        <v>0.3517</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.754</v>
+        <v>-0.6603</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3273</v>
+        <v>-3.8854</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1125</v>
+        <v>-1.9962</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2148</v>
+        <v>-1.8893</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4533</v>
+        <v>0.4347</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.112</v>
+        <v>-0.22</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5653</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8828</v>
+        <v>0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.2764</v>
+        <v>-4.3064</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6896</v>
+        <v>-3.5224</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.5868</v>
+        <v>-0.784</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4947</v>
+        <v>-3.752</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5482</v>
+        <v>-1.9852</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0535</v>
+        <v>-1.7669</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4889</v>
+        <v>-1.4302</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6807</v>
+        <v>-0.2034</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8081</v>
+        <v>-1.2268</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.9836</v>
+        <v>-2.3219</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.229</v>
+        <v>-1.7818</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7546</v>
+        <v>-0.5401</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.2743</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.251</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.434</v>
+        <v>0.1452</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.482</v>
+        <v>-0.416</v>
       </c>
       <c r="U21" t="n">
-        <v>0.916</v>
+        <v>0.5612</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.126099999999999</v>
+        <v>-5.9408</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8612</v>
+        <v>-3.6596</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.2649</v>
+        <v>-2.2812</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2653</v>
+        <v>-2.3625</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6861</v>
+        <v>-0.3937</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5792</v>
+        <v>-1.9688</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2341</v>
+        <v>-0.0352</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1936</v>
+        <v>0.7188</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>-0.754</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.4994</v>
+        <v>-2.3273</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.8798</v>
+        <v>-1.1125</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6196</v>
+        <v>-1.2148</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.7115</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.2975</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1568</v>
+        <v>0.4533</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3012</v>
+        <v>-0.112</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1443</v>
+        <v>0.5653</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9925</v>
+        <v>-1.8828</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4966</v>
+        <v>-0.3869</v>
       </c>
       <c r="X22" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-8.126099999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.8612</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-5.2649</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.2653</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.6861</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.5792</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.2341</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.1936</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-4.4994</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-2.8798</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.6196</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-3.7115</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-4.2975</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.1568</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.3012</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.9925</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.4966</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R. DIAZ DEL VALLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-9.725300000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-5.1385</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.5868</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.9436</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-3.3901</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5535</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.1612</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.2011</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-4.9836</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-3.229</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.7546</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-5.2743</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-6.251</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.482</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484372_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-30.66</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>-12.5831</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>-18.0768</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>-19.6771</v>
       </c>
-      <c r="H23" t="n">
-        <v>-6.862300000000001</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H25" t="n">
+        <v>-6.8623</v>
+      </c>
+      <c r="I25" t="n">
         <v>-12.8148</v>
       </c>
-      <c r="J23" t="n">
-        <v>5.615300000000001</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J25" t="n">
+        <v>5.6153</v>
+      </c>
+      <c r="K25" t="n">
         <v>10.3299</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>-4.714700000000001</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>-25.2925</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-17.1925</v>
       </c>
-      <c r="O23" t="n">
-        <v>-8.100100000000001</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="O25" t="n">
+        <v>-8.100099999999999</v>
+      </c>
+      <c r="P25" t="n">
         <v>-11.7205</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-19.5343</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>7.8137</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>1.9535</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>-2.1037</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>4.0571</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>-1.2157</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W25" t="n">
         <v>3.4395</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-4.6552</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
